--- a/template-siswa.xlsx
+++ b/template-siswa.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Jenis Ibadah</t>
+          <t>Agama</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Muslim</t>
+          <t>Islam</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -493,7 +493,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Non-Muslim</t>
+          <t>Katolik</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Muslim</t>
+          <t>Hindu</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2013,7 +2013,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Jenis ibadah" error="Pilih Muslim atau Non-Muslim" type="list">
-      <formula1>"Muslim,Non-Muslim"</formula1>
+      <formula1>"Islam,Kristen,Katolik,Hindu,Buddha,Konghucu"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2039,9 +2039,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -2066,7 +2064,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>4. Kolom "Jenis Ibadah" wajib diisi: pilih Muslim atau Non-Muslim dari daftar. Baris yang kosong/tidak dikenali dilewati dan dilaporkan.</t>
+          <t>4. Kolom "Agama" wajib diisi: pilih Islam, Kristen, Katolik, Hindu, Buddha, atau Konghucu dari daftar. Baris yang kosong/tidak dikenali dilewati dan dilaporkan.</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2099,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>9. Sandi awal semua siswa: sdn007keren (wajib diganti siswa saat masuk pertama).</t>
+          <t>9. Sandi awal semua siswa yang diimpor: sdn007keren (wajib diganti siswa saat masuk pertama). Cara yang lebih mudah: pakai link pendaftaran mandiri di menu Kelas.</t>
         </is>
       </c>
     </row>
